--- a/Result/profitability/3178.xlsx
+++ b/Result/profitability/3178.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003749999999999948</v>
+        <v>0.07624999999999996</v>
       </c>
       <c r="N2" t="n">
-        <v>14.645</v>
+        <v>15.3375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.008750000000000053</v>
+        <v>0.001249999999999953</v>
       </c>
       <c r="N3" t="n">
-        <v>14.85875</v>
+        <v>15.1925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.78</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.275</v>
+        <v>-0.26875</v>
       </c>
       <c r="N4" t="n">
-        <v>12.94375</v>
+        <v>12.97625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3575</v>
+        <v>-0.2125</v>
       </c>
       <c r="N5" t="n">
-        <v>12.2175</v>
+        <v>13.29375</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.13875</v>
+        <v>-0.08625000000000005</v>
       </c>
       <c r="N6" t="n">
-        <v>13.5475</v>
+        <v>14.48125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.79</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08374999999999996</v>
+        <v>0.1525</v>
       </c>
       <c r="N7" t="n">
-        <v>15.4825</v>
+        <v>16.85</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -7540,6 +7540,135 @@
       </c>
       <c r="AM56" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3178</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>367</v>
+      </c>
+      <c r="D57" t="n">
+        <v>292</v>
+      </c>
+      <c r="E57" t="n">
+        <v>74</v>
+      </c>
+      <c r="F57" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="G57" t="n">
+        <v>25</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>25</v>
+      </c>
+      <c r="K57" t="n">
+        <v>19</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.02124999999999995</v>
+      </c>
+      <c r="N57" t="n">
+        <v>15.02375</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y57" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.4781341107871719</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-1.589041095890411</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>8.610000000000001</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.737789203084833</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
